--- a/excel_sheeets/DK Gupta_LB.xlsx
+++ b/excel_sheeets/DK Gupta_LB.xlsx
@@ -342,16 +342,682 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Count of Publications in each affiliation</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="156082"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="E97132"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="196B24"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0F9ED5"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="A02B93"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4EA72E"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="5B90A8"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="F09C70"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Affiliations!$A$2:$A$9</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Affiliations!$B$2:$B$9</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Number of Citations vs. Year</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="156082"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Citations!$A$10:$A$45</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Citations!$B$10:$B$45</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="521426278"/>
+        <c:axId val="102771001"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="521426278"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="102771001"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="102771001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Number of Citations</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="521426278"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Publisher and Publication Count</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Journals!$A$2:$A$24</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Journals!$B$2:$B$24</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Journals!$A$2:$A$24</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Journals!$C$2:$C$24</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1412657600"/>
+        <c:axId val="257771939"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1412657600"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Journal Name</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="257771939"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="257771939"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1412657600"/>
+        <c:crosses val="max"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:latin typeface="Arial Narrow"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 1" title="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2" title="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -359,7 +1025,33 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="10029825" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 3" title="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
